--- a/research/traditional_assets/database/data/switzerland/switzerland_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_electronics_consumer_office.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.099</v>
       </c>
       <c r="E2">
-        <v>0.174</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="F2">
-        <v>0.0757</v>
+        <v>0.068</v>
       </c>
       <c r="G2">
-        <v>0.4044227734390806</v>
+        <v>0.4567384490951371</v>
       </c>
       <c r="H2">
-        <v>0.2389430664022984</v>
+        <v>0.2777070063694267</v>
       </c>
       <c r="I2">
-        <v>0.2585383985735764</v>
+        <v>0.2187850316761008</v>
       </c>
       <c r="J2">
-        <v>0.2264968008598665</v>
+        <v>0.2025422498436477</v>
       </c>
       <c r="K2">
-        <v>1129.6</v>
+        <v>966.4</v>
       </c>
       <c r="L2">
-        <v>0.2285436814631975</v>
+        <v>0.1954099686583763</v>
       </c>
       <c r="M2">
-        <v>510.2</v>
+        <v>661.2</v>
       </c>
       <c r="N2">
-        <v>0.01948183362926475</v>
+        <v>0.03737979614103919</v>
       </c>
       <c r="O2">
-        <v>0.4516643059490085</v>
+        <v>0.6841887417218544</v>
       </c>
       <c r="P2">
-        <v>479.3</v>
+        <v>527.9</v>
       </c>
       <c r="Q2">
-        <v>0.01830192641808428</v>
+        <v>0.02984391164981033</v>
       </c>
       <c r="R2">
-        <v>0.4243094900849859</v>
+        <v>0.5462541390728477</v>
       </c>
       <c r="S2">
-        <v>30.89999999999998</v>
+        <v>133.3000000000001</v>
       </c>
       <c r="T2">
-        <v>0.06056448451587609</v>
+        <v>0.2016031457955234</v>
       </c>
       <c r="U2">
-        <v>1639.1</v>
+        <v>1082.3</v>
       </c>
       <c r="V2">
-        <v>0.06258854077171278</v>
+        <v>0.06118595487514628</v>
       </c>
       <c r="W2">
-        <v>0.2213036067629253</v>
+        <v>0.1650639657027687</v>
       </c>
       <c r="X2">
-        <v>0.06273570493383168</v>
+        <v>0.1041497033501922</v>
       </c>
       <c r="Y2">
-        <v>0.1585679018290937</v>
+        <v>0.06091426235257655</v>
       </c>
       <c r="Z2">
-        <v>1.241846642111556</v>
+        <v>1.149823975303288</v>
       </c>
       <c r="AA2">
-        <v>0.2812742915968351</v>
+        <v>0.2328879348820948</v>
       </c>
       <c r="AB2">
-        <v>0.06257384410782256</v>
+        <v>0.1038353066573696</v>
       </c>
       <c r="AC2">
-        <v>0.2187004474890125</v>
+        <v>0.1290526282247251</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>99.240556051206</v>
+        <v>85.49312922921771</v>
       </c>
       <c r="AF2">
-        <v>99.240556051206</v>
+        <v>85.49312922921771</v>
       </c>
       <c r="AG2">
-        <v>-1539.859443948794</v>
+        <v>-996.8068707707822</v>
       </c>
       <c r="AH2">
-        <v>0.003775164922964888</v>
+        <v>0.004809958382224755</v>
       </c>
       <c r="AI2">
-        <v>0.01666804616487886</v>
+        <v>0.01433560167779246</v>
       </c>
       <c r="AJ2">
-        <v>-0.06247238830259791</v>
+        <v>-0.05971802377678007</v>
       </c>
       <c r="AK2">
-        <v>-0.3568751669836951</v>
+        <v>-0.2042054070183403</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-28.3</v>
+        <v>-33.5</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.063438842506073</v>
+        <v>-0.7895499966501245</v>
       </c>
       <c r="AQ2">
-        <v>-45.04593639575972</v>
+        <v>-32.11343283582089</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>0.099</v>
       </c>
       <c r="E3">
-        <v>0.174</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="F3">
-        <v>0.0757</v>
+        <v>0.068</v>
       </c>
       <c r="G3">
-        <v>0.4044227734390806</v>
+        <v>0.4567384490951371</v>
       </c>
       <c r="H3">
-        <v>0.2389430664022984</v>
+        <v>0.2777070063694267</v>
       </c>
       <c r="I3">
-        <v>0.2585383985735764</v>
+        <v>0.2187850316761008</v>
       </c>
       <c r="J3">
-        <v>0.2264968008598665</v>
+        <v>0.2025422498436477</v>
       </c>
       <c r="K3">
-        <v>1129.6</v>
+        <v>966.4</v>
       </c>
       <c r="L3">
-        <v>0.2285436814631975</v>
+        <v>0.1954099686583763</v>
       </c>
       <c r="M3">
-        <v>510.2</v>
+        <v>661.2</v>
       </c>
       <c r="N3">
-        <v>0.01948183362926475</v>
+        <v>0.03737979614103919</v>
       </c>
       <c r="O3">
-        <v>0.4516643059490085</v>
+        <v>0.6841887417218544</v>
       </c>
       <c r="P3">
-        <v>479.3</v>
+        <v>527.9</v>
       </c>
       <c r="Q3">
-        <v>0.01830192641808428</v>
+        <v>0.02984391164981033</v>
       </c>
       <c r="R3">
-        <v>0.4243094900849859</v>
+        <v>0.5462541390728477</v>
       </c>
       <c r="S3">
-        <v>30.89999999999998</v>
+        <v>133.3000000000001</v>
       </c>
       <c r="T3">
-        <v>0.06056448451587609</v>
+        <v>0.2016031457955234</v>
       </c>
       <c r="U3">
-        <v>1639.1</v>
+        <v>1082.3</v>
       </c>
       <c r="V3">
-        <v>0.06258854077171278</v>
+        <v>0.06118595487514628</v>
       </c>
       <c r="W3">
-        <v>0.2213036067629253</v>
+        <v>0.1650639657027687</v>
       </c>
       <c r="X3">
-        <v>0.06273570493383168</v>
+        <v>0.1041497033501922</v>
       </c>
       <c r="Y3">
-        <v>0.1585679018290937</v>
+        <v>0.06091426235257655</v>
       </c>
       <c r="Z3">
-        <v>1.241846642111556</v>
+        <v>1.149823975303288</v>
       </c>
       <c r="AA3">
-        <v>0.2812742915968351</v>
+        <v>0.2328879348820948</v>
       </c>
       <c r="AB3">
-        <v>0.06257384410782256</v>
+        <v>0.1038353066573696</v>
       </c>
       <c r="AC3">
-        <v>0.2187004474890125</v>
+        <v>0.1290526282247251</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>99.240556051206</v>
+        <v>85.49312922921771</v>
       </c>
       <c r="AF3">
-        <v>99.240556051206</v>
+        <v>85.49312922921771</v>
       </c>
       <c r="AG3">
-        <v>-1539.859443948794</v>
+        <v>-996.8068707707822</v>
       </c>
       <c r="AH3">
-        <v>0.003775164922964888</v>
+        <v>0.004809958382224755</v>
       </c>
       <c r="AI3">
-        <v>0.01666804616487886</v>
+        <v>0.01433560167779246</v>
       </c>
       <c r="AJ3">
-        <v>-0.06247238830259791</v>
+        <v>-0.05971802377678007</v>
       </c>
       <c r="AK3">
-        <v>-0.3568751669836951</v>
+        <v>-0.2042054070183403</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-28.3</v>
+        <v>-33.5</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.063438842506073</v>
+        <v>-0.7895499966501245</v>
       </c>
       <c r="AQ3">
-        <v>-45.04593639575972</v>
+        <v>-32.11343283582089</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_electronics_consumer_office.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.099</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E2">
-        <v>0.06570000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="F2">
-        <v>0.068</v>
+        <v>0.0687</v>
       </c>
       <c r="G2">
-        <v>0.4567384490951371</v>
+        <v>0.4107005007818531</v>
       </c>
       <c r="H2">
-        <v>0.2777070063694267</v>
+        <v>0.2358821084301577</v>
       </c>
       <c r="I2">
-        <v>0.2187850316761008</v>
+        <v>0.2024089019700603</v>
       </c>
       <c r="J2">
-        <v>0.2025422498436477</v>
+        <v>0.1836359703368538</v>
       </c>
       <c r="K2">
-        <v>966.4</v>
+        <v>1040.8</v>
       </c>
       <c r="L2">
-        <v>0.1954099686583763</v>
+        <v>0.2060133409869163</v>
       </c>
       <c r="M2">
-        <v>661.2</v>
+        <v>891.9000000000001</v>
       </c>
       <c r="N2">
-        <v>0.03737979614103919</v>
+        <v>0.03626538503763159</v>
       </c>
       <c r="O2">
-        <v>0.6841887417218544</v>
+        <v>0.8569369715603383</v>
       </c>
       <c r="P2">
-        <v>527.9</v>
+        <v>699.2</v>
       </c>
       <c r="Q2">
-        <v>0.02984391164981033</v>
+        <v>0.02843004509284898</v>
       </c>
       <c r="R2">
-        <v>0.5462541390728477</v>
+        <v>0.6717909300538049</v>
       </c>
       <c r="S2">
-        <v>133.3000000000001</v>
+        <v>192.7</v>
       </c>
       <c r="T2">
-        <v>0.2016031457955234</v>
+        <v>0.216055611615652</v>
       </c>
       <c r="U2">
-        <v>1082.3</v>
+        <v>1422.9</v>
       </c>
       <c r="V2">
-        <v>0.06118595487514628</v>
+        <v>0.05785628026689763</v>
       </c>
       <c r="W2">
-        <v>0.1650639657027687</v>
+        <v>0.1770610050695791</v>
       </c>
       <c r="X2">
-        <v>0.1041497033501922</v>
+        <v>0.08972554172486674</v>
       </c>
       <c r="Y2">
-        <v>0.06091426235257655</v>
+        <v>0.08733546334471237</v>
       </c>
       <c r="Z2">
-        <v>1.149823975303288</v>
+        <v>1.150754530721117</v>
       </c>
       <c r="AA2">
-        <v>0.2328879348820948</v>
+        <v>0.2113199248685032</v>
       </c>
       <c r="AB2">
-        <v>0.1038353066573696</v>
+        <v>0.08944560439983681</v>
       </c>
       <c r="AC2">
-        <v>0.1290526282247251</v>
+        <v>0.1218743204686664</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>85.49312922921771</v>
+        <v>135.049931785292</v>
       </c>
       <c r="AF2">
-        <v>85.49312922921771</v>
+        <v>135.049931785292</v>
       </c>
       <c r="AG2">
-        <v>-996.8068707707822</v>
+        <v>-1287.850068214708</v>
       </c>
       <c r="AH2">
-        <v>0.004809958382224755</v>
+        <v>0.005461251869092844</v>
       </c>
       <c r="AI2">
-        <v>0.01433560167779246</v>
+        <v>0.02082705794813723</v>
       </c>
       <c r="AJ2">
-        <v>-0.05971802377678007</v>
+        <v>-0.05525866132255042</v>
       </c>
       <c r="AK2">
-        <v>-0.2042054070183403</v>
+        <v>-0.2544429137048588</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-33.5</v>
+        <v>-68.8</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.7895499966501245</v>
+        <v>-1.05276716113358</v>
       </c>
       <c r="AQ2">
-        <v>-32.11343283582089</v>
+        <v>-14.80959302325581</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.099</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E3">
-        <v>0.06570000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="F3">
-        <v>0.068</v>
+        <v>0.0687</v>
       </c>
       <c r="G3">
-        <v>0.4567384490951371</v>
+        <v>0.4107005007818531</v>
       </c>
       <c r="H3">
-        <v>0.2777070063694267</v>
+        <v>0.2358821084301577</v>
       </c>
       <c r="I3">
-        <v>0.2187850316761008</v>
+        <v>0.2024089019700603</v>
       </c>
       <c r="J3">
-        <v>0.2025422498436477</v>
+        <v>0.1836359703368538</v>
       </c>
       <c r="K3">
-        <v>966.4</v>
+        <v>1040.8</v>
       </c>
       <c r="L3">
-        <v>0.1954099686583763</v>
+        <v>0.2060133409869163</v>
       </c>
       <c r="M3">
-        <v>661.2</v>
+        <v>891.9000000000001</v>
       </c>
       <c r="N3">
-        <v>0.03737979614103919</v>
+        <v>0.03626538503763159</v>
       </c>
       <c r="O3">
-        <v>0.6841887417218544</v>
+        <v>0.8569369715603383</v>
       </c>
       <c r="P3">
-        <v>527.9</v>
+        <v>699.2</v>
       </c>
       <c r="Q3">
-        <v>0.02984391164981033</v>
+        <v>0.02843004509284898</v>
       </c>
       <c r="R3">
-        <v>0.5462541390728477</v>
+        <v>0.6717909300538049</v>
       </c>
       <c r="S3">
-        <v>133.3000000000001</v>
+        <v>192.7</v>
       </c>
       <c r="T3">
-        <v>0.2016031457955234</v>
+        <v>0.216055611615652</v>
       </c>
       <c r="U3">
-        <v>1082.3</v>
+        <v>1422.9</v>
       </c>
       <c r="V3">
-        <v>0.06118595487514628</v>
+        <v>0.05785628026689763</v>
       </c>
       <c r="W3">
-        <v>0.1650639657027687</v>
+        <v>0.1770610050695791</v>
       </c>
       <c r="X3">
-        <v>0.1041497033501922</v>
+        <v>0.08972554172486674</v>
       </c>
       <c r="Y3">
-        <v>0.06091426235257655</v>
+        <v>0.08733546334471237</v>
       </c>
       <c r="Z3">
-        <v>1.149823975303288</v>
+        <v>1.150754530721117</v>
       </c>
       <c r="AA3">
-        <v>0.2328879348820948</v>
+        <v>0.2113199248685032</v>
       </c>
       <c r="AB3">
-        <v>0.1038353066573696</v>
+        <v>0.08944560439983681</v>
       </c>
       <c r="AC3">
-        <v>0.1290526282247251</v>
+        <v>0.1218743204686664</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>85.49312922921771</v>
+        <v>135.049931785292</v>
       </c>
       <c r="AF3">
-        <v>85.49312922921771</v>
+        <v>135.049931785292</v>
       </c>
       <c r="AG3">
-        <v>-996.8068707707822</v>
+        <v>-1287.850068214708</v>
       </c>
       <c r="AH3">
-        <v>0.004809958382224755</v>
+        <v>0.005461251869092844</v>
       </c>
       <c r="AI3">
-        <v>0.01433560167779246</v>
+        <v>0.02082705794813723</v>
       </c>
       <c r="AJ3">
-        <v>-0.05971802377678007</v>
+        <v>-0.05525866132255042</v>
       </c>
       <c r="AK3">
-        <v>-0.2042054070183403</v>
+        <v>-0.2544429137048588</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-33.5</v>
+        <v>-68.8</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7895499966501245</v>
+        <v>-1.05276716113358</v>
       </c>
       <c r="AQ3">
-        <v>-32.11343283582089</v>
+        <v>-14.80959302325581</v>
       </c>
     </row>
   </sheetData>
